--- a/Documentación/Brechas/brecha fianzas.xlsx
+++ b/Documentación/Brechas/brecha fianzas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\Global\Documentación\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\Global\Documentación\Brechas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2A104B5-C47C-4ADC-AB56-93F1405E8596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B5C29AB-E135-40D2-9C75-1BFA1E29995A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="8" xr2:uid="{55631BAB-3F43-4C4D-BEDF-0998D0E484F9}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{55631BAB-3F43-4C4D-BEDF-0998D0E484F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Fianza - Emision" sheetId="3" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <sheet name="Reportes matriz" sheetId="11" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -892,7 +893,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -958,21 +959,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="8" tint="-0.499984740745262"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="8" tint="-0.499984740745262"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1001,7 +987,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1049,9 +1035,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1074,59 +1057,48 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
@@ -1563,28 +1535,28 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="28" t="s">
         <v>175</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="28" t="s">
         <v>157</v>
       </c>
-      <c r="C5" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="D5" s="30" t="s">
+      <c r="C5" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="E5" s="29" t="s">
+      <c r="E5" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="F5" s="29" t="s">
+      <c r="F5" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="G5" s="29" t="s">
+      <c r="G5" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="H5" s="32" t="s">
+      <c r="H5" s="30" t="s">
         <v>176</v>
       </c>
     </row>
@@ -1615,80 +1587,80 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="27" t="s">
         <v>134</v>
       </c>
-      <c r="C7" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="F7" s="17" t="s">
+      <c r="C7" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F7" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="G7" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="H7" s="19" t="s">
+      <c r="G7" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="H7" s="29" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="C8" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="D8" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="E8" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="F8" s="29" t="s">
+      <c r="C8" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="G8" s="29" t="s">
-        <v>62</v>
-      </c>
-      <c r="H8" s="31" t="s">
+      <c r="G8" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="H8" s="29" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="C9" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="D9" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="E9" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="F9" s="29" t="s">
+      <c r="C9" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="G9" s="29" t="s">
-        <v>62</v>
-      </c>
-      <c r="H9" s="31" t="s">
+      <c r="G9" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="H9" s="29" t="s">
         <v>144</v>
       </c>
     </row>
@@ -2986,54 +2958,54 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="28" t="s">
         <v>147</v>
       </c>
-      <c r="C3" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="F3" s="17" t="s">
+      <c r="C3" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="G3" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="H3" s="20" t="s">
+      <c r="G3" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="H3" s="30" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="105" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="28" t="s">
         <v>150</v>
       </c>
-      <c r="C4" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="F4" s="17" t="s">
+      <c r="C4" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="G4" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="H4" s="20" t="s">
+      <c r="G4" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="H4" s="30" t="s">
         <v>151</v>
       </c>
     </row>
@@ -3090,80 +3062,80 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="C7" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="F7" s="17" t="s">
+      <c r="C7" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F7" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="G7" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="H7" s="20" t="s">
+      <c r="G7" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="H7" s="30" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="28" t="s">
         <v>155</v>
       </c>
-      <c r="C8" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="D8" s="30" t="s">
+      <c r="C8" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="E8" s="29" t="s">
+      <c r="E8" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="F8" s="29" t="s">
+      <c r="F8" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="G8" s="34" t="s">
+      <c r="G8" s="32" t="s">
         <v>71</v>
       </c>
-      <c r="H8" s="32" t="s">
+      <c r="H8" s="30" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="30" t="s">
+      <c r="A9" s="28" t="s">
         <v>161</v>
       </c>
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="28" t="s">
         <v>155</v>
       </c>
-      <c r="C9" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="D9" s="30" t="s">
+      <c r="C9" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="E9" s="29" t="s">
+      <c r="E9" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="F9" s="29" t="s">
+      <c r="F9" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="G9" s="34" t="s">
+      <c r="G9" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="H9" s="32" t="s">
+      <c r="H9" s="30" t="s">
         <v>160</v>
       </c>
     </row>
@@ -3249,7 +3221,7 @@
       <c r="A13" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="B13" s="35" t="s">
+      <c r="B13" s="33" t="s">
         <v>164</v>
       </c>
       <c r="C13" s="18" t="s">
@@ -3264,10 +3236,10 @@
       <c r="F13" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="G13" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="H13" s="20" t="s">
+      <c r="G13" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="H13" s="19" t="s">
         <v>184</v>
       </c>
     </row>
@@ -3275,7 +3247,7 @@
       <c r="A14" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="B14" s="35" t="s">
+      <c r="B14" s="33" t="s">
         <v>164</v>
       </c>
       <c r="C14" s="18" t="s">
@@ -3290,36 +3262,36 @@
       <c r="F14" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="G14" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="H14" s="20" t="s">
+      <c r="G14" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="H14" s="19" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A15" s="36" t="s">
+      <c r="A15" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="B15" s="37" t="s">
+      <c r="B15" s="34" t="s">
         <v>187</v>
       </c>
-      <c r="C15" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="E15" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="F15" s="38" t="s">
+      <c r="C15" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F15" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="G15" s="39" t="s">
-        <v>62</v>
-      </c>
-      <c r="H15" s="40" t="s">
+      <c r="G15" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="H15" s="30" t="s">
         <v>190</v>
       </c>
     </row>
@@ -3423,80 +3395,80 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" s="18" t="s">
+      <c r="C4" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="F4" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="H4" s="28" t="s">
+      <c r="H4" s="36" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="37" t="s">
         <v>79</v>
       </c>
-      <c r="B5" s="42" t="s">
+      <c r="B5" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="C5" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="D5" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="E5" s="42" t="s">
-        <v>60</v>
-      </c>
-      <c r="F5" s="42" t="s">
+      <c r="C5" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="G5" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="H5" s="43" t="s">
+      <c r="G5" s="38" t="s">
+        <v>62</v>
+      </c>
+      <c r="H5" s="39" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A6" s="41" t="s">
+      <c r="A6" s="37" t="s">
         <v>79</v>
       </c>
-      <c r="B6" s="41" t="s">
+      <c r="B6" s="37" t="s">
         <v>145</v>
       </c>
-      <c r="C6" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="42" t="s">
-        <v>60</v>
-      </c>
-      <c r="F6" s="42" t="s">
+      <c r="C6" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="G6" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="H6" s="44" t="s">
+      <c r="G6" s="38" t="s">
+        <v>62</v>
+      </c>
+      <c r="H6" s="40" t="s">
         <v>178</v>
       </c>
     </row>
@@ -3528,6 +3500,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3575,172 +3548,172 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="C2" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="D2" s="22" t="s">
+      <c r="C2" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="H2" s="23" t="s">
+      <c r="H2" s="22" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="C3" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="F3" s="22" t="s">
+      <c r="C3" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="G3" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="H3" s="24" t="s">
+      <c r="G3" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="H3" s="23" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="F4" s="22" t="s">
+      <c r="C4" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="G4" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="H4" s="24" t="s">
+      <c r="G4" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="H4" s="23" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="D5" s="22" t="s">
+      <c r="C5" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="G5" s="21" t="s">
+      <c r="G5" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="H5" s="24" t="s">
+      <c r="H5" s="23" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="C6" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="F6" s="22" t="s">
+      <c r="C6" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="G6" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="H6" s="24" t="s">
+      <c r="G6" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="H6" s="23" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="C7" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="E7" s="22" t="s">
+      <c r="C7" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="F7" s="22" t="s">
+      <c r="F7" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="G7" s="22" t="s">
+      <c r="G7" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="H7" s="24" t="s">
+      <c r="H7" s="23" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="24"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3913,10 +3886,10 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="25" t="s">
         <v>181</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="26" t="s">
         <v>200</v>
       </c>
       <c r="C8" s="18" t="s">
@@ -3928,9 +3901,9 @@
       <c r="E8" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27" t="s">
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26" t="s">
         <v>201</v>
       </c>
     </row>
@@ -4546,790 +4519,789 @@
   <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.42578125" style="45" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" style="45" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="11.42578125" style="45"/>
+    <col min="1" max="1" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="C1" s="46" t="s">
+      <c r="C1" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="D1" s="46" t="s">
+      <c r="D1" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="E1" s="46" t="s">
+      <c r="E1" s="4" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="45" t="s">
+      <c r="A2" t="s">
         <v>230</v>
       </c>
-      <c r="B2" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C2" s="45">
+      <c r="B2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2">
         <v>81</v>
       </c>
-      <c r="D2" s="45" t="s">
+      <c r="D2" t="s">
         <v>218</v>
       </c>
-      <c r="E2" s="45">
+      <c r="E2">
         <v>305</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="45" t="s">
+      <c r="A3" t="s">
         <v>231</v>
       </c>
-      <c r="B3" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C3" s="45">
+      <c r="B3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C3">
         <v>81</v>
       </c>
-      <c r="D3" s="45" t="s">
+      <c r="D3" t="s">
         <v>216</v>
       </c>
-      <c r="E3" s="45">
+      <c r="E3">
         <v>303</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="45" t="s">
+      <c r="A4" t="s">
         <v>232</v>
       </c>
-      <c r="B4" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C4" s="45">
+      <c r="B4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4">
         <v>81</v>
       </c>
-      <c r="D4" s="45" t="s">
+      <c r="D4" t="s">
         <v>217</v>
       </c>
-      <c r="E4" s="45">
+      <c r="E4">
         <v>304</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="45" t="s">
+      <c r="A5" t="s">
         <v>233</v>
       </c>
-      <c r="B5" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C5" s="45">
+      <c r="B5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5">
         <v>82</v>
       </c>
-      <c r="D5" s="45" t="s">
+      <c r="D5" t="s">
         <v>213</v>
       </c>
-      <c r="E5" s="45">
+      <c r="E5">
         <v>313</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="45" t="s">
+      <c r="A6" t="s">
         <v>234</v>
       </c>
-      <c r="B6" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C6" s="45">
+      <c r="B6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6">
         <v>82</v>
       </c>
-      <c r="D6" s="45" t="s">
+      <c r="D6" t="s">
         <v>213</v>
       </c>
-      <c r="E6" s="45">
+      <c r="E6">
         <v>314</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="45" t="s">
+      <c r="A7" t="s">
         <v>235</v>
       </c>
-      <c r="B7" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C7" s="45">
+      <c r="B7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7">
         <v>82</v>
       </c>
-      <c r="D7" s="45" t="s">
+      <c r="D7" t="s">
         <v>213</v>
       </c>
-      <c r="E7" s="45">
+      <c r="E7">
         <v>315</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="45" t="s">
+      <c r="A8" t="s">
         <v>236</v>
       </c>
-      <c r="B8" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C8" s="45">
+      <c r="B8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8">
         <v>82</v>
       </c>
-      <c r="D8" s="45" t="s">
+      <c r="D8" t="s">
         <v>214</v>
       </c>
-      <c r="E8" s="45">
+      <c r="E8">
         <v>313</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="45" t="s">
+      <c r="A9" t="s">
         <v>237</v>
       </c>
-      <c r="B9" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C9" s="45">
+      <c r="B9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9">
         <v>83</v>
       </c>
-      <c r="D9" s="45" t="s">
+      <c r="D9" t="s">
         <v>219</v>
       </c>
-      <c r="E9" s="45">
+      <c r="E9">
         <v>309</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="45" t="s">
+      <c r="A10" t="s">
         <v>238</v>
       </c>
-      <c r="B10" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C10" s="45">
+      <c r="B10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10">
         <v>83</v>
       </c>
-      <c r="D10" s="45" t="s">
+      <c r="D10" t="s">
         <v>219</v>
       </c>
-      <c r="E10" s="45">
+      <c r="E10">
         <v>310</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="45" t="s">
+      <c r="A11" t="s">
         <v>239</v>
       </c>
-      <c r="B11" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C11" s="45">
+      <c r="B11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11">
         <v>83</v>
       </c>
-      <c r="D11" s="45" t="s">
+      <c r="D11" t="s">
         <v>219</v>
       </c>
-      <c r="E11" s="45">
+      <c r="E11">
         <v>311</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="45" t="s">
+      <c r="A12" t="s">
         <v>240</v>
       </c>
-      <c r="B12" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C12" s="45">
+      <c r="B12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12">
         <v>83</v>
       </c>
-      <c r="D12" s="45" t="s">
+      <c r="D12" t="s">
         <v>219</v>
       </c>
-      <c r="E12" s="45">
+      <c r="E12">
         <v>326</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="45" t="s">
+      <c r="A13" t="s">
         <v>241</v>
       </c>
-      <c r="B13" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C13" s="45">
+      <c r="B13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13">
         <v>83</v>
       </c>
-      <c r="D13" s="45" t="s">
+      <c r="D13" t="s">
         <v>219</v>
       </c>
-      <c r="E13" s="45">
+      <c r="E13">
         <v>327</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="45" t="s">
+      <c r="A14" t="s">
         <v>242</v>
       </c>
-      <c r="B14" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C14" s="45">
+      <c r="B14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14">
         <v>83</v>
       </c>
-      <c r="D14" s="45" t="s">
+      <c r="D14" t="s">
         <v>219</v>
       </c>
-      <c r="E14" s="45">
+      <c r="E14">
         <v>328</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="45" t="s">
+      <c r="A15" t="s">
         <v>231</v>
       </c>
-      <c r="B15" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C15" s="45">
+      <c r="B15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15">
         <v>83</v>
       </c>
-      <c r="D15" s="45" t="s">
+      <c r="D15" t="s">
         <v>227</v>
       </c>
-      <c r="E15" s="45">
+      <c r="E15">
         <v>319</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="45" t="s">
+      <c r="A16" t="s">
         <v>243</v>
       </c>
-      <c r="B16" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C16" s="45">
+      <c r="B16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16">
         <v>83</v>
       </c>
-      <c r="D16" s="45" t="s">
+      <c r="D16" t="s">
         <v>227</v>
       </c>
-      <c r="E16" s="45">
+      <c r="E16">
         <v>321</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="45" t="s">
+      <c r="A17" t="s">
         <v>244</v>
       </c>
-      <c r="B17" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C17" s="45">
+      <c r="B17" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17">
         <v>83</v>
       </c>
-      <c r="D17" s="45" t="s">
+      <c r="D17" t="s">
         <v>224</v>
       </c>
-      <c r="E17" s="45">
+      <c r="E17">
         <v>322</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="45" t="s">
+      <c r="A18" t="s">
         <v>231</v>
       </c>
-      <c r="B18" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C18" s="45">
+      <c r="B18" t="s">
+        <v>88</v>
+      </c>
+      <c r="C18">
         <v>83</v>
       </c>
-      <c r="D18" s="45" t="s">
+      <c r="D18" t="s">
         <v>222</v>
       </c>
-      <c r="E18" s="45">
+      <c r="E18">
         <v>319</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="45" t="s">
+      <c r="A19" t="s">
         <v>243</v>
       </c>
-      <c r="B19" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C19" s="45">
+      <c r="B19" t="s">
+        <v>88</v>
+      </c>
+      <c r="C19">
         <v>83</v>
       </c>
-      <c r="D19" s="45" t="s">
+      <c r="D19" t="s">
         <v>223</v>
       </c>
-      <c r="E19" s="45">
+      <c r="E19">
         <v>321</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="45" t="s">
+      <c r="A20" t="s">
         <v>245</v>
       </c>
-      <c r="B20" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C20" s="45">
+      <c r="B20" t="s">
+        <v>88</v>
+      </c>
+      <c r="C20">
         <v>83</v>
       </c>
-      <c r="D20" s="45" t="s">
+      <c r="D20" t="s">
         <v>226</v>
       </c>
-      <c r="E20" s="45">
+      <c r="E20">
         <v>316</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="45" t="s">
+      <c r="A21" t="s">
         <v>246</v>
       </c>
-      <c r="B21" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C21" s="45">
+      <c r="B21" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21">
         <v>83</v>
       </c>
-      <c r="D21" s="45" t="s">
+      <c r="D21" t="s">
         <v>226</v>
       </c>
-      <c r="E21" s="45">
+      <c r="E21">
         <v>317</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="45" t="s">
+      <c r="A22" t="s">
         <v>247</v>
       </c>
-      <c r="B22" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C22" s="45">
+      <c r="B22" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22">
         <v>83</v>
       </c>
-      <c r="D22" s="45" t="s">
+      <c r="D22" t="s">
         <v>220</v>
       </c>
-      <c r="E22" s="45">
+      <c r="E22">
         <v>306</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="45" t="s">
+      <c r="A23" t="s">
         <v>248</v>
       </c>
-      <c r="B23" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C23" s="45">
+      <c r="B23" t="s">
+        <v>88</v>
+      </c>
+      <c r="C23">
         <v>83</v>
       </c>
-      <c r="D23" s="45" t="s">
+      <c r="D23" t="s">
         <v>220</v>
       </c>
-      <c r="E23" s="45">
+      <c r="E23">
         <v>307</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="45" t="s">
+      <c r="A24" t="s">
         <v>249</v>
       </c>
-      <c r="B24" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C24" s="45">
+      <c r="B24" t="s">
+        <v>88</v>
+      </c>
+      <c r="C24">
         <v>83</v>
       </c>
-      <c r="D24" s="45" t="s">
+      <c r="D24" t="s">
         <v>220</v>
       </c>
-      <c r="E24" s="45">
+      <c r="E24">
         <v>308</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="45" t="s">
+      <c r="A25" t="s">
         <v>250</v>
       </c>
-      <c r="B25" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C25" s="45">
+      <c r="B25" t="s">
+        <v>88</v>
+      </c>
+      <c r="C25">
         <v>83</v>
       </c>
-      <c r="D25" s="45" t="s">
+      <c r="D25" t="s">
         <v>220</v>
       </c>
-      <c r="E25" s="45">
+      <c r="E25">
         <v>323</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="45" t="s">
+      <c r="A26" t="s">
         <v>251</v>
       </c>
-      <c r="B26" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C26" s="45">
+      <c r="B26" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26">
         <v>83</v>
       </c>
-      <c r="D26" s="45" t="s">
+      <c r="D26" t="s">
         <v>220</v>
       </c>
-      <c r="E26" s="45">
+      <c r="E26">
         <v>324</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="45" t="s">
+      <c r="A27" t="s">
         <v>252</v>
       </c>
-      <c r="B27" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C27" s="45">
+      <c r="B27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27">
         <v>83</v>
       </c>
-      <c r="D27" s="45" t="s">
+      <c r="D27" t="s">
         <v>220</v>
       </c>
-      <c r="E27" s="45">
+      <c r="E27">
         <v>325</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="45" t="s">
+      <c r="A28" t="s">
         <v>253</v>
       </c>
-      <c r="B28" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C28" s="45">
+      <c r="B28" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28">
         <v>83</v>
       </c>
-      <c r="D28" s="45" t="s">
+      <c r="D28" t="s">
         <v>215</v>
       </c>
-      <c r="E28" s="45">
+      <c r="E28">
         <v>316</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="45" t="s">
+      <c r="A29" t="s">
         <v>254</v>
       </c>
-      <c r="B29" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C29" s="45">
+      <c r="B29" t="s">
+        <v>88</v>
+      </c>
+      <c r="C29">
         <v>83</v>
       </c>
-      <c r="D29" s="45" t="s">
+      <c r="D29" t="s">
         <v>215</v>
       </c>
-      <c r="E29" s="45">
+      <c r="E29">
         <v>317</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="45" t="s">
+      <c r="A30" t="s">
         <v>254</v>
       </c>
-      <c r="B30" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C30" s="45">
+      <c r="B30" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30">
         <v>83</v>
       </c>
-      <c r="D30" s="45" t="s">
+      <c r="D30" t="s">
         <v>215</v>
       </c>
-      <c r="E30" s="45">
+      <c r="E30">
         <v>318</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="45" t="s">
+      <c r="A31" t="s">
         <v>245</v>
       </c>
-      <c r="B31" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C31" s="45">
+      <c r="B31" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31">
         <v>83</v>
       </c>
-      <c r="D31" s="45" t="s">
+      <c r="D31" t="s">
         <v>221</v>
       </c>
-      <c r="E31" s="45">
+      <c r="E31">
         <v>300</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="45" t="s">
+      <c r="A32" t="s">
         <v>255</v>
       </c>
-      <c r="B32" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C32" s="45">
+      <c r="B32" t="s">
+        <v>88</v>
+      </c>
+      <c r="C32">
         <v>83</v>
       </c>
-      <c r="D32" s="45" t="s">
+      <c r="D32" t="s">
         <v>221</v>
       </c>
-      <c r="E32" s="45">
+      <c r="E32">
         <v>301</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="45" t="s">
+      <c r="A33" t="s">
         <v>256</v>
       </c>
-      <c r="B33" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C33" s="45">
+      <c r="B33" t="s">
+        <v>88</v>
+      </c>
+      <c r="C33">
         <v>83</v>
       </c>
-      <c r="D33" s="45" t="s">
+      <c r="D33" t="s">
         <v>221</v>
       </c>
-      <c r="E33" s="45">
+      <c r="E33">
         <v>302</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="45" t="s">
+      <c r="A34" t="s">
         <v>245</v>
       </c>
-      <c r="B34" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C34" s="45">
+      <c r="B34" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34">
         <v>83</v>
       </c>
-      <c r="D34" s="45" t="s">
+      <c r="D34" t="s">
         <v>221</v>
       </c>
-      <c r="E34" s="45">
+      <c r="E34">
         <v>316</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="45" t="s">
+      <c r="A35" t="s">
         <v>246</v>
       </c>
-      <c r="B35" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C35" s="45">
+      <c r="B35" t="s">
+        <v>88</v>
+      </c>
+      <c r="C35">
         <v>83</v>
       </c>
-      <c r="D35" s="45" t="s">
+      <c r="D35" t="s">
         <v>221</v>
       </c>
-      <c r="E35" s="45">
+      <c r="E35">
         <v>317</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="45" t="s">
+      <c r="A36" t="s">
         <v>257</v>
       </c>
-      <c r="B36" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C36" s="45">
+      <c r="B36" t="s">
+        <v>88</v>
+      </c>
+      <c r="C36">
         <v>83</v>
       </c>
-      <c r="D36" s="45" t="s">
+      <c r="D36" t="s">
         <v>221</v>
       </c>
-      <c r="E36" s="45">
+      <c r="E36">
         <v>318</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="45" t="s">
+      <c r="A37" t="s">
         <v>258</v>
       </c>
-      <c r="B37" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C37" s="45">
+      <c r="B37" t="s">
+        <v>88</v>
+      </c>
+      <c r="C37">
         <v>84</v>
       </c>
-      <c r="D37" s="45" t="s">
+      <c r="D37" t="s">
         <v>210</v>
       </c>
-      <c r="E37" s="45">
+      <c r="E37">
         <v>331</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="45" t="s">
+      <c r="A38" t="s">
         <v>259</v>
       </c>
-      <c r="B38" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C38" s="45">
+      <c r="B38" t="s">
+        <v>88</v>
+      </c>
+      <c r="C38">
         <v>84</v>
       </c>
-      <c r="D38" s="45" t="s">
+      <c r="D38" t="s">
         <v>210</v>
       </c>
-      <c r="E38" s="45">
+      <c r="E38">
         <v>334</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="45" t="s">
+      <c r="A39" t="s">
         <v>260</v>
       </c>
-      <c r="B39" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C39" s="45">
+      <c r="B39" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39">
         <v>84</v>
       </c>
-      <c r="D39" s="45" t="s">
+      <c r="D39" t="s">
         <v>210</v>
       </c>
-      <c r="E39" s="45">
+      <c r="E39">
         <v>341</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="45" t="s">
+      <c r="A40" t="s">
         <v>261</v>
       </c>
-      <c r="B40" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C40" s="45">
+      <c r="B40" t="s">
+        <v>88</v>
+      </c>
+      <c r="C40">
         <v>84</v>
       </c>
-      <c r="D40" s="45" t="s">
+      <c r="D40" t="s">
         <v>210</v>
       </c>
-      <c r="E40" s="45">
+      <c r="E40">
         <v>353</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="45" t="s">
+      <c r="A41" t="s">
         <v>262</v>
       </c>
-      <c r="B41" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C41" s="45">
+      <c r="B41" t="s">
+        <v>88</v>
+      </c>
+      <c r="C41">
         <v>84</v>
       </c>
-      <c r="D41" s="45" t="s">
+      <c r="D41" t="s">
         <v>225</v>
       </c>
-      <c r="E41" s="45">
+      <c r="E41">
         <v>329</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="45" t="s">
+      <c r="A42" t="s">
         <v>231</v>
       </c>
-      <c r="B42" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C42" s="45">
+      <c r="B42" t="s">
+        <v>88</v>
+      </c>
+      <c r="C42">
         <v>84</v>
       </c>
-      <c r="D42" s="45" t="s">
+      <c r="D42" t="s">
         <v>225</v>
       </c>
-      <c r="E42" s="45">
+      <c r="E42">
         <v>331</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="45" t="s">
+      <c r="A43" t="s">
         <v>259</v>
       </c>
-      <c r="B43" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C43" s="45">
+      <c r="B43" t="s">
+        <v>88</v>
+      </c>
+      <c r="C43">
         <v>84</v>
       </c>
-      <c r="D43" s="45" t="s">
+      <c r="D43" t="s">
         <v>225</v>
       </c>
-      <c r="E43" s="45">
+      <c r="E43">
         <v>334</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="45" t="s">
+      <c r="A44" t="s">
         <v>263</v>
       </c>
-      <c r="B44" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C44" s="45">
+      <c r="B44" t="s">
+        <v>88</v>
+      </c>
+      <c r="C44">
         <v>84</v>
       </c>
-      <c r="D44" s="45" t="s">
+      <c r="D44" t="s">
         <v>225</v>
       </c>
-      <c r="E44" s="45">
+      <c r="E44">
         <v>337</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="45" t="s">
+      <c r="A45" t="s">
         <v>264</v>
       </c>
-      <c r="B45" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C45" s="45">
+      <c r="B45" t="s">
+        <v>88</v>
+      </c>
+      <c r="C45">
         <v>84</v>
       </c>
-      <c r="D45" s="45" t="s">
+      <c r="D45" t="s">
         <v>225</v>
       </c>
-      <c r="E45" s="45">
+      <c r="E45">
         <v>340</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="45" t="s">
+      <c r="A46" t="s">
         <v>265</v>
       </c>
-      <c r="B46" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C46" s="45">
+      <c r="B46" t="s">
+        <v>88</v>
+      </c>
+      <c r="C46">
         <v>84</v>
       </c>
-      <c r="D46" s="45" t="s">
+      <c r="D46" t="s">
         <v>225</v>
       </c>
-      <c r="E46" s="45">
+      <c r="E46">
         <v>341</v>
       </c>
     </row>

--- a/Documentación/Brechas/brecha fianzas.xlsx
+++ b/Documentación/Brechas/brecha fianzas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\Global\Documentación\Brechas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B5C29AB-E135-40D2-9C75-1BFA1E29995A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0315348-7D7D-4B9B-9BB3-93BB6C62ACB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{55631BAB-3F43-4C4D-BEDF-0998D0E484F9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{55631BAB-3F43-4C4D-BEDF-0998D0E484F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Fianza - Emision" sheetId="3" r:id="rId1"/>
@@ -24,7 +24,6 @@
     <sheet name="Reportes matriz" sheetId="11" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -987,7 +986,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1087,17 +1086,14 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2157,54 +2153,54 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="B29" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F29" s="6" t="s">
+      <c r="B29" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="C29" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="D29" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="E29" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="F29" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="G29" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="H29" s="10" t="s">
+      <c r="G29" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="H29" s="39" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="B30" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F30" s="6" t="s">
+      <c r="B30" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="E30" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="F30" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="G30" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="H30" s="10" t="s">
+      <c r="G30" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="H30" s="39" t="s">
         <v>108</v>
       </c>
     </row>
@@ -3421,54 +3417,54 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A5" s="37" t="s">
+      <c r="A5" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="B5" s="38" t="s">
+      <c r="B5" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="C5" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="D5" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="E5" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="F5" s="38" t="s">
+      <c r="C5" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="G5" s="38" t="s">
-        <v>62</v>
-      </c>
-      <c r="H5" s="39" t="s">
+      <c r="G5" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="H5" s="36" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="28" t="s">
         <v>145</v>
       </c>
-      <c r="C6" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="F6" s="38" t="s">
+      <c r="C6" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="G6" s="38" t="s">
-        <v>62</v>
-      </c>
-      <c r="H6" s="40" t="s">
+      <c r="G6" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="H6" s="30" t="s">
         <v>178</v>
       </c>
     </row>
